--- a/product_selector_out/STM32F405-415.xlsx
+++ b/product_selector_out/STM32F405-415.xlsx
@@ -7787,7 +7787,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.8(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F405-415.xlsx
+++ b/product_selector_out/STM32F405-415.xlsx
@@ -4747,14 +4747,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="8" t="inlineStr">
@@ -4777,9 +4777,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="8" t="inlineStr">
@@ -5114,9 +5114,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -5451,9 +5451,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
@@ -5758,14 +5758,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -5788,9 +5788,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="8" t="inlineStr">
@@ -6125,9 +6125,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="8" t="inlineStr">
@@ -6432,14 +6432,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
@@ -6462,9 +6462,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -6799,9 +6799,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -7106,14 +7106,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
@@ -7136,9 +7136,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -7443,14 +7443,14 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
@@ -7473,9 +7473,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="8" t="inlineStr">

--- a/product_selector_out/STM32F405-415.xlsx
+++ b/product_selector_out/STM32F405-415.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO20"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.671875" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f405oe.pdf</t>
         </is>
       </c>
@@ -1681,6 +1693,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f415og.pdf</t>
         </is>
       </c>
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f415og.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f405oe.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f415og.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f405oe.pdf</t>
         </is>
       </c>
@@ -3366,6 +3403,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f415og.pdf</t>
         </is>
       </c>
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f405oe.pdf</t>
         </is>
       </c>
@@ -4040,12 +4087,17 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f405oe.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4068,12 +4120,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4088,9 +4142,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -4135,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO20"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4205,6 +4258,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4548,6 +4602,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4645,6 +4704,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4977,7 +5037,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5314,7 +5379,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5651,7 +5721,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5988,7 +6063,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6325,7 +6405,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6662,7 +6747,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6999,7 +7089,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7336,7 +7431,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7673,7 +7773,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7681,8 +7786,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
